--- a/author.xlsx
+++ b/author.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32B490A-4FA3-4CF5-896C-E812A987A7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
-    <sheet name="Student 1" sheetId="1" r:id="rId2"/>
-    <sheet name="Student 2" sheetId="2" r:id="rId3"/>
-    <sheet name="Student 3" sheetId="3" r:id="rId4"/>
+    <sheet name="Student 1 " sheetId="5" r:id="rId2"/>
+    <sheet name="Student 2" sheetId="1" r:id="rId3"/>
+    <sheet name="Student 3" sheetId="2" r:id="rId4"/>
+    <sheet name="Student 4" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="63">
   <si>
     <t>&lt;Project Name&gt;</t>
   </si>
@@ -178,13 +180,46 @@
   </si>
   <si>
     <t>&lt;name of the github project&gt;</t>
+  </si>
+  <si>
+    <t>&lt;09.07.2003&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Wasserwerksweg 20&gt;</t>
+  </si>
+  <si>
+    <t>&lt;26603 Aurich&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;Fachbereich Technik&gt;  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;Hochschule Emden/Leer&gt; </t>
+  </si>
+  <si>
+    <t>&lt;01627919295&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janssen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bjarne Rieken </t>
+  </si>
+  <si>
+    <t>bjarieja</t>
+  </si>
+  <si>
+    <t>bjarne.rieken.janssen@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt;5&gt; </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +259,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -242,10 +285,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -260,8 +304,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -539,35 +585,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -583,22 +629,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9A317F-BA04-4C66-888E-704A86A364D1}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" customWidth="1"/>
+    <col min="6" max="6" width="33.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
@@ -618,7 +666,257 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7025719</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45594</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A21" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A37" s="5"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A44" s="5"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{FE6BAEF6-AB3F-4563-8826-FB2F41011170}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A3:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -629,15 +927,15 @@
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -645,7 +943,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>32</v>
       </c>
@@ -653,7 +951,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
@@ -661,12 +959,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
@@ -674,7 +972,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
@@ -682,12 +980,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
@@ -695,7 +993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>9</v>
       </c>
@@ -703,7 +1001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>11</v>
       </c>
@@ -711,17 +1009,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>14</v>
       </c>
@@ -729,7 +1027,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>15</v>
       </c>
@@ -737,12 +1035,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
@@ -750,7 +1048,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
@@ -758,7 +1056,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>42</v>
       </c>
@@ -766,15 +1064,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
@@ -782,7 +1080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>16</v>
       </c>
@@ -790,7 +1088,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>20</v>
       </c>
@@ -798,21 +1096,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
@@ -820,7 +1118,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>16</v>
       </c>
@@ -828,7 +1126,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>20</v>
       </c>
@@ -836,13 +1134,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>24</v>
       </c>
@@ -852,33 +1150,33 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
@@ -898,7 +1196,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -909,15 +1207,15 @@
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -925,7 +1223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>32</v>
       </c>
@@ -933,7 +1231,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
@@ -941,12 +1239,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
@@ -954,7 +1252,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
@@ -962,12 +1260,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
@@ -975,7 +1273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>9</v>
       </c>
@@ -983,7 +1281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>11</v>
       </c>
@@ -991,17 +1289,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>14</v>
       </c>
@@ -1009,7 +1307,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>15</v>
       </c>
@@ -1017,12 +1315,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
@@ -1030,7 +1328,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
@@ -1038,7 +1336,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>42</v>
       </c>
@@ -1046,15 +1344,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
@@ -1062,7 +1360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>16</v>
       </c>
@@ -1070,7 +1368,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>20</v>
       </c>
@@ -1078,21 +1376,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
@@ -1100,7 +1398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>16</v>
       </c>
@@ -1108,7 +1406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>20</v>
       </c>
@@ -1116,13 +1414,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>24</v>
       </c>
@@ -1132,8 +1430,8 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0200-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1141,23 +1439,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
@@ -1177,7 +1475,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1188,15 +1486,15 @@
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1204,7 +1502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>32</v>
       </c>
@@ -1212,7 +1510,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
@@ -1220,12 +1518,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
@@ -1233,7 +1531,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
@@ -1241,12 +1539,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
@@ -1254,7 +1552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>9</v>
       </c>
@@ -1262,7 +1560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>11</v>
       </c>
@@ -1270,17 +1568,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>14</v>
       </c>
@@ -1288,7 +1586,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>15</v>
       </c>
@@ -1296,12 +1594,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
@@ -1309,7 +1607,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
@@ -1317,7 +1615,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>42</v>
       </c>
@@ -1325,15 +1623,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
@@ -1341,7 +1639,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>16</v>
       </c>
@@ -1349,7 +1647,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>20</v>
       </c>
@@ -1357,21 +1655,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
@@ -1379,7 +1677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>16</v>
       </c>
@@ -1387,7 +1685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>20</v>
       </c>
@@ -1395,13 +1693,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>24</v>
       </c>
@@ -1411,11 +1709,17 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0300-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{defa4170-0d19-0005-0004-bc88714345d2}" enabled="1" method="Standard" siteId="{4f455e02-c0f5-4dd7-8284-c56491661975}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/author.xlsx
+++ b/author.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32B490A-4FA3-4CF5-896C-E812A987A7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EB3EF0-50B6-4938-A783-EE0FE71D402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="23040" windowHeight="13560" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Student 2" sheetId="1" r:id="rId3"/>
     <sheet name="Student 3" sheetId="2" r:id="rId4"/>
     <sheet name="Student 4" sheetId="3" r:id="rId5"/>
+    <sheet name="Student 5" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="63">
   <si>
     <t>&lt;Project Name&gt;</t>
   </si>
@@ -298,13 +299,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -590,11 +591,11 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -602,11 +603,11 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -679,7 +680,7 @@
       <c r="D5" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1718,6 +1719,285 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F073ACE-FF11-45CE-85D4-7A87D83169C5}">
+  <dimension ref="A3:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1234567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1">
+        <v>45351</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45594</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A21" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A37" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A44" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{BF81F0CA-8E60-419A-87E7-40832B91426E}">
+      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{D90132FD-8413-423A-A34C-FBCAB40156A2}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{defa4170-0d19-0005-0004-bc88714345d2}" enabled="1" method="Standard" siteId="{4f455e02-c0f5-4dd7-8284-c56491661975}" contentBits="0" removed="0"/>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9833F4-58A7-2343-854F-5A53FDCA90B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F47313-38FE-4415-82E9-3B9EC0FF83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="85">
   <si>
     <t>Short Description</t>
   </si>
@@ -264,6 +264,33 @@
   </si>
   <si>
     <t>&lt;0171 1509226&gt;</t>
+  </si>
+  <si>
+    <t>Cassens</t>
+  </si>
+  <si>
+    <t>Aiko</t>
+  </si>
+  <si>
+    <t>AikCas</t>
+  </si>
+  <si>
+    <t>aiko.cassens@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>aiko.cassens713@gmail.com</t>
+  </si>
+  <si>
+    <t>&lt;23.04.2001&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Schnedermannstraße 52&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;Fachbereich Technik&gt; </t>
+  </si>
+  <si>
+    <t>&lt;017647306591&gt;</t>
   </si>
 </sst>
 </file>
@@ -638,36 +665,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="90.6640625" customWidth="1"/>
+    <col min="3" max="3" width="90.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="33.5" x14ac:dyDescent="0.75">
       <c r="A1" s="7" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -685,22 +712,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9A317F-BA04-4C66-888E-704A86A364D1}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="3" width="33.1640625" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.5" customWidth="1"/>
-    <col min="6" max="6" width="33.1640625" customWidth="1"/>
+    <col min="1" max="1" width="47.36328125" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="33.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.453125" customWidth="1"/>
+    <col min="6" max="6" width="33.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -720,7 +747,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -737,10 +764,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -748,7 +775,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -756,7 +783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -764,7 +791,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -772,12 +799,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -785,7 +812,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -793,12 +820,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -806,7 +833,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -814,7 +841,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -822,17 +849,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -840,7 +867,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -848,12 +875,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -861,7 +888,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -869,7 +896,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -877,49 +904,49 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -940,22 +967,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="3" width="33.1640625" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.36328125" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="33.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -975,7 +1002,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -995,10 +1022,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -1006,7 +1033,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1014,7 +1041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1022,7 +1049,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1030,7 +1057,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -1038,7 +1065,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1046,7 +1073,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,12 +1081,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1067,7 +1094,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1075,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -1083,17 +1110,17 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1101,7 +1128,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1109,12 +1136,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -1122,7 +1149,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -1130,7 +1157,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -1138,49 +1165,49 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -1202,20 +1229,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1235,42 +1262,54 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7025848</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1278,41 +1317,44 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1320,25 +1362,25 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1346,7 +1388,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1354,118 +1396,79 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="A37" s="5"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="A44" s="5"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1474,6 +1477,10 @@
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{445A2FFD-35BB-49FD-BB7C-117547758E88}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{145DE6A8-C4C0-46E7-9F89-73EC07D1F09D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1481,20 +1488,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1514,7 +1521,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1525,15 +1532,15 @@
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1541,7 +1548,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1549,7 +1556,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1557,12 +1564,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1570,7 +1577,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,12 +1585,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1591,7 +1598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1599,7 +1606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -1607,17 +1614,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1625,7 +1632,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1633,12 +1640,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -1646,7 +1653,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -1654,7 +1661,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -1662,15 +1669,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>43</v>
       </c>
@@ -1678,7 +1685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
@@ -1686,7 +1693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
@@ -1694,21 +1701,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
@@ -1716,7 +1723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -1724,7 +1731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
@@ -1732,13 +1739,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
@@ -1760,20 +1767,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F073ACE-FF11-45CE-85D4-7A87D83169C5}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1793,7 +1800,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1804,15 +1811,15 @@
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1820,7 +1827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1828,7 +1835,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1836,12 +1843,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1849,7 +1856,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1857,12 +1864,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1870,7 +1877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1878,7 +1885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -1886,17 +1893,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1904,7 +1911,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1912,12 +1919,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -1925,7 +1932,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -1933,7 +1940,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -1941,15 +1948,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>43</v>
       </c>
@@ -1957,7 +1964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
@@ -1965,7 +1972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
@@ -1973,21 +1980,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
@@ -1995,7 +2002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2003,7 +2010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
@@ -2011,13 +2018,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>23</v>
       </c>

--- a/author.xlsx
+++ b/author.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F47313-38FE-4415-82E9-3B9EC0FF83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE7CEAF-E44D-44EB-8C3A-FB5E0A049E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="93">
   <si>
     <t>Short Description</t>
   </si>
@@ -291,6 +291,30 @@
   </si>
   <si>
     <t>&lt;017647306591&gt;</t>
+  </si>
+  <si>
+    <t>Kröger</t>
+  </si>
+  <si>
+    <t>Jenik</t>
+  </si>
+  <si>
+    <t>Jenik-t1ao</t>
+  </si>
+  <si>
+    <t>jenik.kroeger@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>jenikkroeger@gmail.com</t>
+  </si>
+  <si>
+    <t>Dosfeld 4</t>
+  </si>
+  <si>
+    <t>26904 Börger</t>
+  </si>
+  <si>
+    <t>&lt;0157 3781 4055&gt;</t>
   </si>
 </sst>
 </file>
@@ -665,36 +689,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="90.6328125" customWidth="1"/>
+    <col min="3" max="3" width="90.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="7" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -712,22 +736,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9A317F-BA04-4C66-888E-704A86A364D1}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.36328125" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="33.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" customWidth="1"/>
-    <col min="6" max="6" width="33.1796875" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.21875" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" customWidth="1"/>
+    <col min="6" max="6" width="33.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -747,7 +771,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -764,10 +788,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -775,7 +799,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -783,7 +807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -791,7 +815,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -799,12 +823,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -812,7 +836,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,12 +844,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -833,7 +857,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -841,7 +865,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -849,17 +873,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -867,7 +891,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -875,12 +899,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -888,7 +912,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -896,7 +920,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -904,49 +928,49 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -967,22 +991,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.36328125" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="33.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.21875" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1002,7 +1026,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -1022,10 +1046,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -1033,7 +1057,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1041,7 +1065,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1049,7 +1073,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1057,7 +1081,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -1065,7 +1089,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1073,7 +1097,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,12 +1105,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1094,7 +1118,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1102,7 +1126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -1110,17 +1134,17 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1128,7 +1152,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1136,12 +1160,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -1149,7 +1173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -1157,7 +1181,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -1165,49 +1189,49 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -1229,20 +1253,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1262,7 +1286,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1282,10 +1306,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -1293,7 +1317,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1301,7 +1325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1309,7 +1333,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1317,7 +1341,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -1325,7 +1349,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1333,7 +1357,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,12 +1365,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1354,7 +1378,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1362,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -1370,17 +1394,17 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1388,7 +1412,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1396,12 +1420,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -1409,7 +1433,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -1417,7 +1441,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -1425,49 +1449,49 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -1488,20 +1512,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1521,42 +1545,54 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>7025641</v>
+      </c>
+      <c r="D5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1564,67 +1600,70 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="B19" s="1">
+        <v>37971</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1632,7 +1671,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1640,118 +1679,79 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
-      <c r="A37" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A37" s="5"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A44" s="5"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1760,6 +1760,10 @@
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{9C8DC986-C5A3-4FA7-93CE-14A986852D9A}"/>
+    <hyperlink ref="F5" r:id="rId2" display="jenikkroeger@gmail.com4" xr:uid="{A3B83FA7-E8AC-4F67-93C7-C01AABF96D52}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1767,20 +1771,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F073ACE-FF11-45CE-85D4-7A87D83169C5}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1800,7 +1804,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1811,15 +1815,15 @@
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1827,7 +1831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1835,7 +1839,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1843,12 +1847,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1856,7 +1860,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,12 +1868,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1877,7 +1881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1885,7 +1889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -1893,17 +1897,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1911,7 +1915,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1919,12 +1923,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -1932,7 +1936,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -1940,7 +1944,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -1948,15 +1952,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>43</v>
       </c>
@@ -1964,7 +1968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
@@ -1972,7 +1976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
@@ -1980,21 +1984,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
@@ -2002,7 +2006,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2010,7 +2014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
@@ -2018,13 +2022,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>23</v>
       </c>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE7CEAF-E44D-44EB-8C3A-FB5E0A049E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2890BE96-5978-2D46-A7BE-F5B021C7E9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="93">
   <si>
     <t>Short Description</t>
   </si>
@@ -140,9 +140,6 @@
     <t>CPs:</t>
   </si>
   <si>
-    <t xml:space="preserve"> &lt;5&gt; or &lt;10&gt;</t>
-  </si>
-  <si>
     <t>&lt;Mechanical Engineering Department&gt;</t>
   </si>
   <si>
@@ -315,6 +312,9 @@
   </si>
   <si>
     <t>&lt;0157 3781 4055&gt;</t>
+  </si>
+  <si>
+    <t>&lt;11.03.2026&gt;</t>
   </si>
 </sst>
 </file>
@@ -689,38 +689,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="90.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.6" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -736,22 +736,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9A317F-BA04-4C66-888E-704A86A364D1}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.21875" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.44140625" customWidth="1"/>
-    <col min="6" max="6" width="33.21875" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5" customWidth="1"/>
+    <col min="6" max="6" width="33.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -762,44 +762,44 @@
         <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
         <v>56</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
       </c>
       <c r="C5" s="2">
         <v>7025719</v>
       </c>
       <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -807,7 +807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -815,7 +815,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -823,75 +823,78 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -899,78 +902,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -991,22 +994,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.21875" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1017,47 +1020,47 @@
         <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2">
         <v>7024741</v>
       </c>
       <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1065,7 +1068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1073,7 +1076,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1081,44 +1084,44 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1126,33 +1129,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1160,78 +1163,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -1253,20 +1256,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1277,47 +1280,47 @@
         <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
         <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
       </c>
       <c r="C5" s="2">
         <v>7025848</v>
       </c>
       <c r="D5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1325,15 +1328,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1341,44 +1344,44 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1386,33 +1389,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1420,78 +1423,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -1512,20 +1515,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1536,47 +1539,47 @@
         <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
         <v>85</v>
-      </c>
-      <c r="B5" t="s">
-        <v>86</v>
       </c>
       <c r="C5" s="2">
         <v>7025641</v>
       </c>
       <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1584,7 +1587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1592,7 +1595,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1600,15 +1603,15 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1616,7 +1619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1624,54 +1627,54 @@
         <v>37971</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1679,78 +1682,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
     </row>
   </sheetData>
@@ -1771,20 +1774,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F073ACE-FF11-45CE-85D4-7A87D83169C5}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1795,16 +1798,16 @@
         <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1815,15 +1818,15 @@
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1831,7 +1834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1839,7 +1842,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1847,20 +1850,20 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1868,12 +1871,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1881,7 +1884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1889,7 +1892,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -1897,25 +1900,25 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1923,52 +1926,52 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
         <v>37</v>
       </c>
-      <c r="B33" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="B34" t="s">
         <v>39</v>
       </c>
-      <c r="B34" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="B35" t="s">
         <v>41</v>
       </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
@@ -1976,7 +1979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
@@ -1984,29 +1987,29 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2014,7 +2017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
@@ -2022,13 +2025,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>23</v>
       </c>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10322"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2890BE96-5978-2D46-A7BE-F5B021C7E9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39513C39-9136-B140-BC87-3667D89C9B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="94">
   <si>
     <t>Short Description</t>
   </si>
@@ -50,18 +50,12 @@
     <t>Date of birth:</t>
   </si>
   <si>
-    <t>&lt;01.01.2000&gt;</t>
-  </si>
-  <si>
     <t>Address:</t>
   </si>
   <si>
     <t>Street home:</t>
   </si>
   <si>
-    <t>&lt;Steinweg 15&gt;</t>
-  </si>
-  <si>
     <t>City home:</t>
   </si>
   <si>
@@ -122,12 +116,6 @@
     <t>Matrikelnumber</t>
   </si>
   <si>
-    <t>Wings</t>
-  </si>
-  <si>
-    <t>Elmar</t>
-  </si>
-  <si>
     <t>Study Course:</t>
   </si>
   <si>
@@ -315,6 +303,21 @@
   </si>
   <si>
     <t>&lt;11.03.2026&gt;</t>
+  </si>
+  <si>
+    <t>Ahrens</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>jan.ahrens@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>&lt;31.12.2001&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Friedrich-Ebert-Straße 3&gt;</t>
   </si>
 </sst>
 </file>
@@ -696,7 +699,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -708,19 +711,19 @@
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -753,39 +756,39 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2">
         <v>7025719</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -793,10 +796,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -809,7 +812,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1">
         <v>46092</v>
@@ -817,7 +820,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
@@ -825,18 +828,18 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -844,91 +847,91 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -1011,42 +1014,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2">
         <v>7024741</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1054,10 +1057,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -1070,7 +1073,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1">
         <v>46092</v>
@@ -1078,7 +1081,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
@@ -1086,18 +1089,18 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1105,91 +1108,91 @@
         <v>3</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -1271,42 +1274,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>7025848</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1314,10 +1317,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -1330,15 +1333,15 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
@@ -1346,18 +1349,18 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1365,91 +1368,91 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -1530,42 +1533,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C5" s="2">
         <v>7025641</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1573,10 +1576,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -1589,7 +1592,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1">
         <v>46092</v>
@@ -1597,7 +1600,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
@@ -1605,15 +1608,15 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1629,86 +1632,86 @@
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -1789,33 +1792,36 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
+        <v>7024846</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1823,7 +1829,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -1831,20 +1837,20 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
@@ -1852,15 +1858,15 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1868,91 +1874,91 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -1960,31 +1966,31 @@
     </row>
     <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -1998,31 +2004,31 @@
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -2033,10 +2039,10 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2046,6 +2052,9 @@
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{D90132FD-8413-423A-A34C-FBCAB40156A2}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{D62489D3-CC77-1040-979B-1DDCF2071746}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
